--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-observation-labresult.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3646" uniqueCount="653">
   <si>
     <t>Property</t>
   </si>
@@ -835,7 +835,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -1173,9 +1173,6 @@
     <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Observation.code.coding.display</t>
   </si>
   <si>
@@ -1259,7 +1256,7 @@
     <t>診察や入院など、このObservationが実施されるきっかけとなった診療イベントに関する情報</t>
   </si>
   <si>
-    <t>この検査が行われるヘルスケアイベント。医療提供者と患者の接点。</t>
+    <t>この検査が行われる診療イベント。医療提供者と患者の接点。</t>
   </si>
   <si>
     <t>【JP Core仕様】入院外来の区別や所在場所、担当診療科の情報に使用する。  
@@ -8140,9 +8137,7 @@
       <c r="M48" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="N48" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>317</v>
       </c>
@@ -8228,10 +8223,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8262,9 +8257,7 @@
       <c r="M49" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>326</v>
       </c>
@@ -8350,10 +8343,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8382,10 +8375,10 @@
         <v>333</v>
       </c>
       <c r="M50" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>336</v>
@@ -8472,10 +8465,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8504,10 +8497,10 @@
         <v>275</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O51" t="s" s="2">
         <v>278</v>
@@ -8594,10 +8587,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8620,19 +8613,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8681,7 +8674,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8696,19 +8689,19 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8716,10 +8709,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8742,16 +8735,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="N53" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8801,7 +8794,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8825,10 +8818,10 @@
         <v>351</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8836,14 +8829,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8862,19 +8855,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8923,7 +8916,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8938,19 +8931,19 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8958,14 +8951,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8984,19 +8977,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9045,7 +9038,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9060,19 +9053,19 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9080,10 +9073,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9106,16 +9099,16 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9165,7 +9158,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9186,13 +9179,13 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9200,10 +9193,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9226,19 +9219,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9287,7 +9280,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9302,19 +9295,19 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9322,10 +9315,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9348,19 +9341,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9397,17 +9390,17 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9416,7 +9409,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9425,30 +9418,30 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>83</v>
@@ -9470,19 +9463,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="N59" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9531,7 +9524,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9540,7 +9533,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9549,30 +9542,30 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C60" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>83</v>
@@ -9597,16 +9590,16 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>456</v>
-      </c>
       <c r="O60" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9655,7 +9648,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9664,7 +9657,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9673,30 +9666,30 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C61" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>83</v>
@@ -9721,16 +9714,16 @@
         <v>162</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>460</v>
-      </c>
       <c r="O61" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9779,7 +9772,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9788,7 +9781,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9797,27 +9790,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9843,16 +9836,16 @@
         <v>184</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9880,11 +9873,11 @@
         <v>189</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9901,7 +9894,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9910,7 +9903,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9925,7 +9918,7 @@
         <v>137</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9936,14 +9929,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9965,16 +9958,16 @@
         <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10002,11 +9995,11 @@
         <v>189</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>477</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
       </c>
@@ -10023,7 +10016,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10041,27 +10034,27 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10084,19 +10077,19 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10145,7 +10138,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10166,10 +10159,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10180,10 +10173,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10298,10 +10291,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10418,10 +10411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10444,16 +10437,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10503,7 +10496,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10527,7 +10520,7 @@
         <v>137</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10538,10 +10531,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10564,13 +10557,13 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10621,7 +10614,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10645,7 +10638,7 @@
         <v>137</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10656,10 +10649,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10682,16 +10675,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10741,7 +10734,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>94</v>
@@ -10765,7 +10758,7 @@
         <v>137</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10776,10 +10769,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10805,13 +10798,13 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>514</v>
-      </c>
       <c r="N70" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10837,14 +10830,14 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Y70" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Y70" t="s" s="2">
+      <c r="Z70" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
       </c>
@@ -10861,7 +10854,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10879,27 +10872,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>521</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10925,16 +10918,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10959,14 +10952,14 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>528</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10983,7 +10976,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11004,10 +10997,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11018,10 +11011,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11044,16 +11037,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11103,7 +11096,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11121,27 +11114,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>539</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11164,16 +11157,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11223,7 +11216,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11241,27 +11234,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AN73" t="s" s="2">
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>548</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11284,19 +11277,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11345,7 +11338,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11357,19 +11350,19 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AK74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11380,10 +11373,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11498,10 +11491,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11618,14 +11611,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11647,10 +11640,10 @@
         <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>143</v>
@@ -11705,7 +11698,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11740,10 +11733,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11766,16 +11759,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11825,7 +11818,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11834,7 +11827,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11846,10 +11839,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11860,10 +11853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11886,16 +11879,16 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>575</v>
-      </c>
       <c r="N79" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11945,7 +11938,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11954,7 +11947,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11966,10 +11959,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11980,10 +11973,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12009,16 +12002,16 @@
         <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12046,11 +12039,11 @@
         <v>118</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>583</v>
-      </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
       </c>
@@ -12067,7 +12060,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12085,13 +12078,13 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AM80" t="s" s="2">
-        <v>585</v>
-      </c>
       <c r="AN80" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12102,10 +12095,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12131,16 +12124,16 @@
         <v>184</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12165,14 +12158,14 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y81" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z81" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="Z81" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
       </c>
@@ -12189,7 +12182,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12207,13 +12200,13 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AM81" t="s" s="2">
-        <v>585</v>
-      </c>
       <c r="AN81" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12224,10 +12217,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12250,19 +12243,19 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12311,7 +12304,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12335,7 +12328,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12346,10 +12339,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12375,14 +12368,12 @@
         <v>162</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12431,7 +12422,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12452,10 +12443,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12466,10 +12457,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12492,16 +12483,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12551,7 +12542,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12572,10 +12563,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12586,10 +12577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12612,16 +12603,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12671,7 +12662,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12692,10 +12683,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12706,10 +12697,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12732,19 +12723,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12793,7 +12784,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12814,10 +12805,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12828,10 +12819,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12946,10 +12937,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13066,14 +13057,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13095,10 +13086,10 @@
         <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>143</v>
@@ -13153,7 +13144,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13188,10 +13179,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13217,13 +13208,13 @@
         <v>184</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>346</v>
@@ -13251,14 +13242,14 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>632</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
       </c>
@@ -13275,7 +13266,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -13293,7 +13284,7 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>351</v>
@@ -13310,10 +13301,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13336,19 +13327,19 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="N91" t="s" s="2">
-        <v>638</v>
-      </c>
       <c r="O91" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13397,7 +13388,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13415,27 +13406,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP91" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13461,16 +13452,16 @@
         <v>184</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="N92" t="s" s="2">
-        <v>643</v>
-      </c>
       <c r="O92" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13498,11 +13489,11 @@
         <v>189</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13519,7 +13510,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13528,7 +13519,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13543,7 +13534,7 @@
         <v>137</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13554,14 +13545,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13583,16 +13574,16 @@
         <v>184</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13620,11 +13611,11 @@
         <v>189</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="Z93" t="s" s="2">
-        <v>477</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
       </c>
@@ -13641,7 +13632,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13659,27 +13650,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13705,16 +13696,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13763,7 +13754,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13784,10 +13775,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
